--- a/artfynd/A 16271-2026 artfynd.xlsx
+++ b/artfynd/A 16271-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114883326</v>
+        <v>114883166</v>
       </c>
       <c r="B2" t="n">
-        <v>57916</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,11 +708,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -729,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617219</v>
+        <v>617331</v>
       </c>
       <c r="R2" t="n">
-        <v>6778429</v>
+        <v>6778456</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-12</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -795,42 +785,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114884427</v>
+        <v>114884225</v>
       </c>
       <c r="B3" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -844,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617351</v>
+        <v>617337</v>
       </c>
       <c r="R3" t="n">
-        <v>6778463</v>
+        <v>6778471</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -910,42 +895,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114884225</v>
+        <v>114884427</v>
       </c>
       <c r="B4" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -959,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617337</v>
+        <v>617351</v>
       </c>
       <c r="R4" t="n">
-        <v>6778471</v>
+        <v>6778463</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1025,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114883166</v>
+        <v>114883129</v>
       </c>
       <c r="B5" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,16 +1016,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1074,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>617331</v>
+        <v>617403</v>
       </c>
       <c r="R5" t="n">
-        <v>6778456</v>
+        <v>6778488</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,12 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-03-29</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1112,342 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114883326</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Fårskär, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>617219</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6778429</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114883327</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Fårskär, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>617335</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6778396</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114881247</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Fårskär, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>617388</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6778439</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderhamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Söderala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16271-2026 artfynd.xlsx
+++ b/artfynd/A 16271-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883166</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884225</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114884427</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883129</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883326</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1342,6 +1372,11 @@
           <t>Storgrundet Nät - Koncessionsansökan Gävle</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114883327</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,8 +1483,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114881247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>